--- a/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A61985-C523-41DC-9D1D-A869D1AD63E9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F60F1D8-E4D2-45F7-8FED-BD52F22D61D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="77">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>APRIL 2026</t>
+  </si>
+  <si>
+    <t>04/21/2026</t>
   </si>
 </sst>
 </file>
@@ -2371,7 +2374,9 @@
       <c r="B7" s="23">
         <v>1</v>
       </c>
-      <c r="C7" s="19"/>
+      <c r="C7" s="19" t="s">
+        <v>76</v>
+      </c>
       <c r="D7" s="20" t="s">
         <v>68</v>
       </c>
@@ -2379,22 +2384,27 @@
       <c r="F7" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="20"/>
+      <c r="G7" s="20">
+        <v>518567067</v>
+      </c>
       <c r="H7" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I7" s="21"/>
+      <c r="I7" s="21">
+        <f>1389888-197458.95</f>
+        <v>1192429.05</v>
+      </c>
       <c r="K7" s="21">
         <f>M7*12</f>
-        <v>0</v>
+        <v>127760.25535714286</v>
       </c>
       <c r="L7" s="27">
         <f>I7-K7</f>
-        <v>0</v>
+        <v>1064668.7946428573</v>
       </c>
       <c r="M7" s="33">
         <f>I7/112</f>
-        <v>0</v>
+        <v>10646.687946428572</v>
       </c>
       <c r="N7" s="26"/>
       <c r="O7" s="26"/>
@@ -3127,20 +3137,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>0</v>
+        <v>1192429.05</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>0</v>
+        <v>127760.25535714286</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>0</v>
+        <v>1064668.7946428573</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>0</v>
+        <v>10646.687946428572</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F60F1D8-E4D2-45F7-8FED-BD52F22D61D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB04AE1-B679-4B96-AAAB-97BD6C2DC585}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="79">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -264,6 +264,12 @@
   </si>
   <si>
     <t>04/21/2026</t>
+  </si>
+  <si>
+    <t>04/22/2026</t>
+  </si>
+  <si>
+    <t>04/23/2026</t>
   </si>
 </sst>
 </file>
@@ -2418,7 +2424,9 @@
         <f>B7+1</f>
         <v>2</v>
       </c>
-      <c r="C8" s="19"/>
+      <c r="C8" s="19" t="s">
+        <v>77</v>
+      </c>
       <c r="D8" s="20" t="s">
         <v>68</v>
       </c>
@@ -2426,22 +2434,27 @@
       <c r="F8" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="20"/>
+      <c r="G8" s="20">
+        <v>518571189</v>
+      </c>
       <c r="H8" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="21"/>
+      <c r="I8" s="21">
+        <f>1397196-60845.09</f>
+        <v>1336350.9099999999</v>
+      </c>
       <c r="K8" s="21">
         <f>M8*12</f>
-        <v>0</v>
+        <v>143180.45464285713</v>
       </c>
       <c r="L8" s="27">
         <f>I8-K8</f>
-        <v>0</v>
+        <v>1193170.4553571427</v>
       </c>
       <c r="M8" s="33">
         <f t="shared" ref="M8:M26" si="0">I8/112</f>
-        <v>0</v>
+        <v>11931.704553571428</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -2453,7 +2466,9 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="C9" s="19"/>
+      <c r="C9" s="19" t="s">
+        <v>78</v>
+      </c>
       <c r="D9" s="20" t="s">
         <v>68</v>
       </c>
@@ -2461,22 +2476,27 @@
       <c r="F9" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="20">
+        <v>518575196</v>
+      </c>
       <c r="H9" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="21"/>
+      <c r="I9" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K9" s="21">
         <f t="shared" ref="K9:K26" si="2">M9*12</f>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L9" s="27">
         <f t="shared" ref="L9:L26" si="3">I9-K9</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M9" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -2488,7 +2508,9 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="C10" s="19"/>
+      <c r="C10" s="19" t="s">
+        <v>78</v>
+      </c>
       <c r="D10" s="20" t="s">
         <v>68</v>
       </c>
@@ -2496,22 +2518,27 @@
       <c r="F10" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="20">
+        <v>518574796</v>
+      </c>
       <c r="H10" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="21"/>
+      <c r="I10" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K10" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L10" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M10" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -3137,20 +3164,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>1192429.05</v>
+        <v>5201481.88</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>127760.25535714286</v>
+        <v>557301.62999999989</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>1064668.7946428573</v>
+        <v>4644180.25</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>10646.687946428572</v>
+        <v>46441.802500000005</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB04AE1-B679-4B96-AAAB-97BD6C2DC585}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F78E4A2-D854-4CF0-9C0E-28C1C190B498}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="80">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>04/23/2026</t>
+  </si>
+  <si>
+    <t>04/24/2026</t>
   </si>
 </sst>
 </file>
@@ -2550,7 +2553,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="C11" s="19"/>
+      <c r="C11" s="19" t="s">
+        <v>79</v>
+      </c>
       <c r="D11" s="20" t="s">
         <v>68</v>
       </c>
@@ -2558,22 +2563,27 @@
       <c r="F11" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="20"/>
+      <c r="G11" s="20">
+        <v>518579559</v>
+      </c>
       <c r="H11" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="21"/>
+      <c r="I11" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K11" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L11" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M11" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -2585,7 +2595,9 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="C12" s="19"/>
+      <c r="C12" s="19" t="s">
+        <v>79</v>
+      </c>
       <c r="D12" s="20" t="s">
         <v>68</v>
       </c>
@@ -2593,22 +2605,27 @@
       <c r="F12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="20">
+        <v>518578932</v>
+      </c>
       <c r="H12" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I12" s="21"/>
+      <c r="I12" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K12" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L12" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M12" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -3164,20 +3181,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>5201481.88</v>
+        <v>7874183.7999999998</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>557301.62999999989</v>
+        <v>843662.54999999981</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>4644180.25</v>
+        <v>7030521.25</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>46441.802500000005</v>
+        <v>70305.212500000009</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F78E4A2-D854-4CF0-9C0E-28C1C190B498}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0540F9-CD43-4D67-8DDB-F3360EAA4278}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="81">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>04/24/2026</t>
+  </si>
+  <si>
+    <t>04/28/2026</t>
   </si>
 </sst>
 </file>
@@ -2637,7 +2640,9 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="C13" s="19"/>
+      <c r="C13" s="19" t="s">
+        <v>80</v>
+      </c>
       <c r="D13" s="20" t="s">
         <v>68</v>
       </c>
@@ -2645,22 +2650,27 @@
       <c r="F13" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="20"/>
+      <c r="G13" s="20">
+        <v>518591718</v>
+      </c>
       <c r="H13" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I13" s="21"/>
+      <c r="I13" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K13" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L13" s="27">
         <f>I13-K13</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M13" s="33">
         <f>I13/112</f>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -2672,7 +2682,9 @@
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="C14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>80</v>
+      </c>
       <c r="D14" s="20" t="s">
         <v>68</v>
       </c>
@@ -2680,22 +2692,27 @@
       <c r="F14" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="20"/>
+      <c r="G14" s="20">
+        <v>518592064</v>
+      </c>
       <c r="H14" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="37"/>
+      <c r="I14" s="37">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K14" s="21">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="L14" s="27">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="M14" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -3181,20 +3198,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>7874183.7999999998</v>
+        <v>10546885.719999999</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>843662.54999999981</v>
+        <v>1130023.4699999997</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>7030521.25</v>
+        <v>9416862.25</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>70305.212500000009</v>
+        <v>94168.622500000012</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">

--- a/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0540F9-CD43-4D67-8DDB-F3360EAA4278}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EB21FB-4FFD-43BB-AEEC-AC44CB85850D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="82">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>04/28/2026</t>
+  </si>
+  <si>
+    <t>04/29/2026</t>
   </si>
 </sst>
 </file>
@@ -2489,15 +2492,15 @@
         <v>74</v>
       </c>
       <c r="I9" s="21">
-        <f>1397196-60845.04</f>
+        <f t="shared" ref="I9:I14" si="2">1397196-60845.04</f>
         <v>1336350.96</v>
       </c>
       <c r="K9" s="21">
-        <f t="shared" ref="K9:K26" si="2">M9*12</f>
+        <f t="shared" ref="K9:K26" si="3">M9*12</f>
         <v>143180.46</v>
       </c>
       <c r="L9" s="27">
-        <f t="shared" ref="L9:L26" si="3">I9-K9</f>
+        <f t="shared" ref="L9:L26" si="4">I9-K9</f>
         <v>1193170.5</v>
       </c>
       <c r="M9" s="33">
@@ -2531,15 +2534,15 @@
         <v>74</v>
       </c>
       <c r="I10" s="21">
-        <f>1397196-60845.04</f>
+        <f t="shared" si="2"/>
         <v>1336350.96</v>
       </c>
       <c r="K10" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143180.46</v>
       </c>
       <c r="L10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1193170.5</v>
       </c>
       <c r="M10" s="33">
@@ -2573,15 +2576,15 @@
         <v>74</v>
       </c>
       <c r="I11" s="21">
-        <f>1397196-60845.04</f>
+        <f t="shared" si="2"/>
         <v>1336350.96</v>
       </c>
       <c r="K11" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143180.46</v>
       </c>
       <c r="L11" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1193170.5</v>
       </c>
       <c r="M11" s="33">
@@ -2615,15 +2618,15 @@
         <v>74</v>
       </c>
       <c r="I12" s="21">
-        <f>1397196-60845.04</f>
+        <f t="shared" si="2"/>
         <v>1336350.96</v>
       </c>
       <c r="K12" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143180.46</v>
       </c>
       <c r="L12" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1193170.5</v>
       </c>
       <c r="M12" s="33">
@@ -2657,11 +2660,11 @@
         <v>74</v>
       </c>
       <c r="I13" s="21">
-        <f>1397196-60845.04</f>
+        <f t="shared" si="2"/>
         <v>1336350.96</v>
       </c>
       <c r="K13" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143180.46</v>
       </c>
       <c r="L13" s="27">
@@ -2699,15 +2702,15 @@
         <v>74</v>
       </c>
       <c r="I14" s="37">
-        <f>1397196-60845.04</f>
+        <f t="shared" si="2"/>
         <v>1336350.96</v>
       </c>
       <c r="K14" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143180.46</v>
       </c>
       <c r="L14" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1193170.5</v>
       </c>
       <c r="M14" s="33">
@@ -2724,7 +2727,9 @@
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="C15" s="19"/>
+      <c r="C15" s="19" t="s">
+        <v>81</v>
+      </c>
       <c r="D15" s="20" t="s">
         <v>68</v>
       </c>
@@ -2732,22 +2737,27 @@
       <c r="F15" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="20">
+        <v>518598013</v>
+      </c>
       <c r="H15" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I15" s="21"/>
+      <c r="I15" s="21">
+        <f>1397196-87924.62</f>
+        <v>1309271.3799999999</v>
+      </c>
       <c r="K15" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>140279.07642857142</v>
       </c>
       <c r="L15" s="27">
         <f>I15-K15</f>
-        <v>0</v>
+        <v>1168992.3035714284</v>
       </c>
       <c r="M15" s="33">
         <f>I15/112</f>
-        <v>0</v>
+        <v>11689.923035714284</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -2759,7 +2769,9 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="19" t="s">
+        <v>81</v>
+      </c>
       <c r="D16" s="20" t="s">
         <v>68</v>
       </c>
@@ -2767,22 +2779,27 @@
       <c r="F16" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="20">
+        <v>518596521</v>
+      </c>
       <c r="H16" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I16" s="21"/>
+      <c r="I16" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K16" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>143180.46</v>
       </c>
       <c r="L16" s="27">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1193170.5</v>
       </c>
       <c r="M16" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
@@ -2794,7 +2811,9 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="C17" s="19"/>
+      <c r="C17" s="19" t="s">
+        <v>81</v>
+      </c>
       <c r="D17" s="20" t="s">
         <v>68</v>
       </c>
@@ -2802,22 +2821,27 @@
       <c r="F17" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="20"/>
+      <c r="G17" s="20">
+        <v>518596660</v>
+      </c>
       <c r="H17" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I17" s="21"/>
+      <c r="I17" s="21">
+        <f>1397196-60845.04</f>
+        <v>1336350.96</v>
+      </c>
       <c r="K17" s="21">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>143180.46</v>
       </c>
       <c r="L17" s="27">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>1193170.5</v>
       </c>
       <c r="M17" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -2843,11 +2867,11 @@
       </c>
       <c r="I18" s="21"/>
       <c r="K18" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L18" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M18" s="33">
@@ -2878,11 +2902,11 @@
       </c>
       <c r="I19" s="21"/>
       <c r="K19" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M19" s="33">
@@ -2913,11 +2937,11 @@
       </c>
       <c r="I20" s="21"/>
       <c r="K20" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L20" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M20" s="33">
@@ -2948,11 +2972,11 @@
       </c>
       <c r="I21" s="21"/>
       <c r="K21" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M21" s="33">
@@ -2983,11 +3007,11 @@
       </c>
       <c r="I22" s="21"/>
       <c r="K22" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M22" s="33">
@@ -3018,11 +3042,11 @@
       </c>
       <c r="I23" s="21"/>
       <c r="K23" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L23" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M23" s="33">
@@ -3053,11 +3077,11 @@
       </c>
       <c r="I24" s="21"/>
       <c r="K24" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L24" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M24" s="33">
@@ -3088,11 +3112,11 @@
       </c>
       <c r="I25" s="21"/>
       <c r="K25" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L25" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M25" s="33">
@@ -3123,11 +3147,11 @@
       </c>
       <c r="I26" s="21"/>
       <c r="K26" s="21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L26" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M26" s="33">
@@ -3158,15 +3182,15 @@
       </c>
       <c r="I27" s="21"/>
       <c r="K27" s="21">
-        <f t="shared" ref="K27" si="4">M27*12</f>
+        <f t="shared" ref="K27" si="5">M27*12</f>
         <v>0</v>
       </c>
       <c r="L27" s="27">
-        <f t="shared" ref="L27" si="5">I27-K27</f>
+        <f t="shared" ref="L27" si="6">I27-K27</f>
         <v>0</v>
       </c>
       <c r="M27" s="33">
-        <f t="shared" ref="M27" si="6">I27/112</f>
+        <f t="shared" ref="M27" si="7">I27/112</f>
         <v>0</v>
       </c>
     </row>
@@ -3198,20 +3222,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>10546885.719999999</v>
+        <v>14528859.02</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>1130023.4699999997</v>
+        <v>1556663.4664285711</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>9416862.25</v>
+        <v>12972195.553571429</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>94168.622500000012</v>
+        <v>129721.9555357143</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
@@ -3336,7 +3360,7 @@
       <c r="H40" s="20"/>
       <c r="I40" s="21"/>
       <c r="K40" s="21">
-        <f t="shared" ref="K40:K59" si="7">M40*12</f>
+        <f t="shared" ref="K40:K59" si="8">M40*12</f>
         <v>0</v>
       </c>
       <c r="L40" s="27">
@@ -3344,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="33">
-        <f t="shared" ref="M40:M59" si="8">I40/112</f>
+        <f t="shared" ref="M40:M59" si="9">I40/112</f>
         <v>0</v>
       </c>
     </row>
@@ -3360,15 +3384,15 @@
       <c r="H41" s="20"/>
       <c r="I41" s="21"/>
       <c r="K41" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L41" s="27">
-        <f t="shared" ref="L41:L59" si="9">I41-K41</f>
+        <f t="shared" ref="L41:L59" si="10">I41-K41</f>
         <v>0</v>
       </c>
       <c r="M41" s="33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -3384,15 +3408,15 @@
       <c r="H42" s="20"/>
       <c r="I42" s="21"/>
       <c r="K42" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L42" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M42" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3408,15 +3432,15 @@
       <c r="H43" s="20"/>
       <c r="I43" s="21"/>
       <c r="K43" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L43" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M43" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3432,15 +3456,15 @@
       <c r="H44" s="20"/>
       <c r="I44" s="21"/>
       <c r="K44" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L44" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M44" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3456,15 +3480,15 @@
       <c r="H45" s="20"/>
       <c r="I45" s="21"/>
       <c r="K45" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L45" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M45" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M45" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3480,15 +3504,15 @@
       <c r="H46" s="20"/>
       <c r="I46" s="21"/>
       <c r="K46" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L46" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M46" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M46" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3504,15 +3528,15 @@
       <c r="H47" s="20"/>
       <c r="I47" s="21"/>
       <c r="K47" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L47" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M47" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M47" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3528,15 +3552,15 @@
       <c r="H48" s="20"/>
       <c r="I48" s="21"/>
       <c r="K48" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L48" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M48" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3552,15 +3576,15 @@
       <c r="H49" s="20"/>
       <c r="I49" s="21"/>
       <c r="K49" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L49" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M49" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M49" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3576,15 +3600,15 @@
       <c r="H50" s="20"/>
       <c r="I50" s="21"/>
       <c r="K50" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L50" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M50" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M50" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3600,15 +3624,15 @@
       <c r="H51" s="20"/>
       <c r="I51" s="21"/>
       <c r="K51" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L51" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M51" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M51" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3624,15 +3648,15 @@
       <c r="H52" s="20"/>
       <c r="I52" s="21"/>
       <c r="K52" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L52" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M52" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M52" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3648,15 +3672,15 @@
       <c r="H53" s="20"/>
       <c r="I53" s="21"/>
       <c r="K53" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L53" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M53" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M53" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3672,15 +3696,15 @@
       <c r="H54" s="20"/>
       <c r="I54" s="21"/>
       <c r="K54" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L54" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M54" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M54" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3696,15 +3720,15 @@
       <c r="H55" s="20"/>
       <c r="I55" s="21"/>
       <c r="K55" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L55" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M55" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M55" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3720,15 +3744,15 @@
       <c r="H56" s="20"/>
       <c r="I56" s="21"/>
       <c r="K56" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L56" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M56" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M56" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3744,15 +3768,15 @@
       <c r="H57" s="20"/>
       <c r="I57" s="21"/>
       <c r="K57" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L57" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M57" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M57" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3768,15 +3792,15 @@
       <c r="H58" s="20"/>
       <c r="I58" s="21"/>
       <c r="K58" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L58" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M58" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M58" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -3792,15 +3816,15 @@
       <c r="H59" s="20"/>
       <c r="I59" s="21"/>
       <c r="K59" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L59" s="27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="M59" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M59" s="33">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>

--- a/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/PURCHASES - APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EB21FB-4FFD-43BB-AEEC-AC44CB85850D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A302831-DEE3-466A-9096-7EE570058BE1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="83">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>04/29/2026</t>
+  </si>
+  <si>
+    <t>04/30/2026</t>
   </si>
 </sst>
 </file>
@@ -2853,7 +2856,9 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="C18" s="19"/>
+      <c r="C18" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="D18" s="20" t="s">
         <v>68</v>
       </c>
@@ -2861,22 +2866,27 @@
       <c r="F18" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="20"/>
+      <c r="G18" s="20">
+        <v>518601437</v>
+      </c>
       <c r="H18" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I18" s="21"/>
+      <c r="I18" s="21">
+        <f>1595030-71899</f>
+        <v>1523131</v>
+      </c>
       <c r="K18" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>163192.60714285716</v>
       </c>
       <c r="L18" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1359938.3928571427</v>
       </c>
       <c r="M18" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13599.383928571429</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -2888,7 +2898,9 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="C19" s="19"/>
+      <c r="C19" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="D19" s="20" t="s">
         <v>68</v>
       </c>
@@ -2896,22 +2908,27 @@
       <c r="F19" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="20"/>
+      <c r="G19" s="20">
+        <v>518601395</v>
+      </c>
       <c r="H19" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="21"/>
+      <c r="I19" s="21">
+        <f>1338502-58774.06</f>
+        <v>1279727.94</v>
+      </c>
       <c r="K19" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>137113.70785714284</v>
       </c>
       <c r="L19" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1142614.232142857</v>
       </c>
       <c r="M19" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11426.142321428571</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
@@ -2923,7 +2940,9 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="C20" s="19"/>
+      <c r="C20" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="D20" s="20" t="s">
         <v>68</v>
       </c>
@@ -2931,22 +2950,27 @@
       <c r="F20" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="20"/>
+      <c r="G20" s="20">
+        <v>518602149</v>
+      </c>
       <c r="H20" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I20" s="21"/>
+      <c r="I20" s="21">
+        <f>1408992-61129.98</f>
+        <v>1347862.02</v>
+      </c>
       <c r="K20" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>144413.78785714286</v>
       </c>
       <c r="L20" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1203448.2321428573</v>
       </c>
       <c r="M20" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12034.482321428572</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
@@ -2958,7 +2982,9 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="C21" s="19"/>
+      <c r="C21" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="D21" s="20" t="s">
         <v>68</v>
       </c>
@@ -2966,22 +2992,27 @@
       <c r="F21" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="20"/>
+      <c r="G21" s="20">
+        <v>518602662</v>
+      </c>
       <c r="H21" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I21" s="21"/>
+      <c r="I21" s="21">
+        <f>1388076-60442.05</f>
+        <v>1327633.95</v>
+      </c>
       <c r="K21" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>142246.49464285714</v>
       </c>
       <c r="L21" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1185387.4553571427</v>
       </c>
       <c r="M21" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11853.874553571428</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
@@ -2993,7 +3024,9 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C22" s="19"/>
+      <c r="C22" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="D22" s="20" t="s">
         <v>68</v>
       </c>
@@ -3001,22 +3034,27 @@
       <c r="F22" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G22" s="20"/>
+      <c r="G22" s="20">
+        <v>518602686</v>
+      </c>
       <c r="H22" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I22" s="21"/>
+      <c r="I22" s="21">
+        <f>173455-21781.45</f>
+        <v>151673.54999999999</v>
+      </c>
       <c r="K22" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>16250.737499999999</v>
       </c>
       <c r="L22" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>135422.8125</v>
       </c>
       <c r="M22" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1354.2281249999999</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -3028,7 +3066,9 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="C23" s="19"/>
+      <c r="C23" s="19" t="s">
+        <v>82</v>
+      </c>
       <c r="D23" s="20" t="s">
         <v>68</v>
       </c>
@@ -3036,22 +3076,27 @@
       <c r="F23" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G23" s="20"/>
+      <c r="G23" s="20">
+        <v>518602635</v>
+      </c>
       <c r="H23" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="21"/>
+      <c r="I23" s="21">
+        <f>1449144-64424.16</f>
+        <v>1384719.84</v>
+      </c>
       <c r="K23" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>148362.84000000003</v>
       </c>
       <c r="L23" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1236357</v>
       </c>
       <c r="M23" s="33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12363.570000000002</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
@@ -3222,20 +3267,20 @@
       <c r="G32"/>
       <c r="I32" s="46">
         <f>SUM(I7:I31)</f>
-        <v>14528859.02</v>
+        <v>21543607.32</v>
       </c>
       <c r="J32" s="47"/>
       <c r="K32" s="46">
         <f>SUM(K7:K31)</f>
-        <v>1556663.4664285711</v>
+        <v>2308243.6414285707</v>
       </c>
       <c r="L32" s="46">
         <f>SUM(L7:L31)</f>
-        <v>12972195.553571429</v>
+        <v>19235363.678571425</v>
       </c>
       <c r="M32" s="48">
         <f>SUM(M7:M31)</f>
-        <v>129721.9555357143</v>
+        <v>192353.63678571431</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
